--- a/inputData/Experiments/inputDataEx5_10_25.xlsx
+++ b/inputData/Experiments/inputDataEx5_10_25.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\Experiments\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/Experiments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{615043A3-1538-4AC1-9737-CDCA65FDB9D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A958A67E-54C1-C349-B1DF-68EF6017289A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16340" activeTab="3" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="PlaneData" sheetId="7" r:id="rId1"/>
     <sheet name="Infrastructure" sheetId="1" r:id="rId2"/>
     <sheet name="PassengerGroups" sheetId="2" r:id="rId3"/>
+    <sheet name="PassengerGroupsB" sheetId="8" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
   <si>
     <t>type</t>
   </si>
@@ -116,7 +117,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -514,12 +515,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94FE46B-0EE8-4D7E-956E-06AD6DDE4FF5}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -527,7 +528,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -535,7 +536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -543,7 +544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -551,7 +552,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -559,7 +560,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -567,7 +568,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -575,7 +576,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -583,7 +584,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -591,7 +592,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -599,7 +600,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -615,14 +616,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3245F359-CA05-2247-86C6-92433A84B0A2}">
   <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="3" max="3" width="22.5" customWidth="1"/>
-    <col min="4" max="4" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -636,7 +637,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -653,7 +654,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -670,7 +671,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -687,7 +688,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -704,7 +705,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -721,10 +722,10 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:5">
       <c r="E18" s="4"/>
     </row>
-    <row r="20" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:5">
       <c r="D20" s="4"/>
     </row>
   </sheetData>
@@ -736,13 +737,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0891C305-141D-384C-BB9E-30507F3FCDCC}">
   <dimension ref="A1:X32"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="5" max="5" width="11.875" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" customWidth="1"/>
     <col min="6" max="6" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -762,7 +763,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>1</v>
       </c>
@@ -782,7 +783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
@@ -802,7 +803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>3</v>
       </c>
@@ -822,7 +823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>4</v>
       </c>
@@ -842,7 +843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>5</v>
       </c>
@@ -862,7 +863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>6</v>
       </c>
@@ -882,7 +883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>7</v>
       </c>
@@ -902,7 +903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>8</v>
       </c>
@@ -922,7 +923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>9</v>
       </c>
@@ -942,7 +943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>10</v>
       </c>
@@ -962,7 +963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>11</v>
       </c>
@@ -982,7 +983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1002,7 +1003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1022,7 +1023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1042,7 +1043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1062,7 +1063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1082,7 +1083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1102,7 +1103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1122,7 +1123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1142,7 +1143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1162,7 +1163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1182,7 +1183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1208,7 +1209,7 @@
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1240,7 +1241,7 @@
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1272,7 +1273,7 @@
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1304,7 +1305,7 @@
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24">
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
@@ -1318,7 +1319,7 @@
       <c r="W27" s="3"/>
       <c r="X27" s="3"/>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24">
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
@@ -1332,7 +1333,7 @@
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24">
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
@@ -1346,7 +1347,7 @@
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24">
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
@@ -1360,7 +1361,7 @@
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24">
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
@@ -1374,7 +1375,7 @@
       <c r="W31" s="3"/>
       <c r="X31" s="3"/>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24">
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
@@ -1391,4 +1392,534 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8605F2F0-FF3A-9E4E-8DB6-AA30D745D8DF}">
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>62</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>17</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>108</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>35</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>91</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>44</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>76</v>
+      </c>
+      <c r="E8">
+        <v>4</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>5</v>
+      </c>
+      <c r="D9">
+        <v>23</v>
+      </c>
+      <c r="E9">
+        <v>3</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>4</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10">
+        <v>57</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>3</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>84</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>12</v>
+      </c>
+      <c r="E12">
+        <v>4</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>5</v>
+      </c>
+      <c r="D13">
+        <v>69</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>4</v>
+      </c>
+      <c r="D14">
+        <v>101</v>
+      </c>
+      <c r="E14">
+        <v>3</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>4</v>
+      </c>
+      <c r="C15">
+        <v>5</v>
+      </c>
+      <c r="D15">
+        <v>28</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16">
+        <v>73</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>5</v>
+      </c>
+      <c r="C17">
+        <v>4</v>
+      </c>
+      <c r="D17">
+        <v>39</v>
+      </c>
+      <c r="E17">
+        <v>3</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18">
+        <v>3</v>
+      </c>
+      <c r="D18">
+        <v>96</v>
+      </c>
+      <c r="E18">
+        <v>2</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <v>15</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>4</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>52</v>
+      </c>
+      <c r="E20">
+        <v>3</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>3</v>
+      </c>
+      <c r="C21">
+        <v>4</v>
+      </c>
+      <c r="D21">
+        <v>110</v>
+      </c>
+      <c r="E21">
+        <v>2</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>5</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>31</v>
+      </c>
+      <c r="E22">
+        <v>4</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <v>3</v>
+      </c>
+      <c r="D23">
+        <v>88</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>2</v>
+      </c>
+      <c r="C24">
+        <v>4</v>
+      </c>
+      <c r="D24">
+        <v>47</v>
+      </c>
+      <c r="E24">
+        <v>3</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>4</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25">
+        <v>66</v>
+      </c>
+      <c r="E25">
+        <v>2</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>3</v>
+      </c>
+      <c r="C26">
+        <v>5</v>
+      </c>
+      <c r="D26">
+        <v>21</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>